--- a/data/trans_dic/IP22D2_R_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP22D2_R_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 27,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,66</t>
+          <t>0,0; 15,87</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>618</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3549</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2870</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2942</t>
+          <t>0; 3595</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>618</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3632</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3750</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3796</t>
+          <t>0; 3567</t>
         </is>
       </c>
     </row>
